--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486926_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486926_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2213</v>
+        <v>4.8489</v>
       </c>
       <c r="E2" t="n">
-        <v>4.585</v>
+        <v>5.2126</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3638</v>
@@ -610,10 +610,10 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7323</v>
+        <v>1.3599</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0272</v>
+        <v>0.6004</v>
       </c>
       <c r="U2" t="n">
         <v>0.7596000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6997</v>
+        <v>2.0888</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9808</v>
+        <v>1.7256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7189</v>
+        <v>0.3632</v>
       </c>
       <c r="G3" t="n">
         <v>1.8645</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6299</v>
+        <v>1.019</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8286</v>
+        <v>0.5733</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8014</v>
+        <v>0.4457</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5893</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9248</v>
+        <v>1.8482</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0961</v>
+        <v>0.7823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8288</v>
+        <v>1.0659</v>
       </c>
       <c r="G4" t="n">
         <v>0.5502</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>0.929</v>
+        <v>0.8524</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.6857</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0704</v>
+        <v>0.1667</v>
       </c>
       <c r="V4" t="n">
         <v>0.2402</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7428</v>
+        <v>1.2724</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3152</v>
+        <v>-0.3651</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5725</v>
+        <v>1.6374</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5523</v>
+        <v>-1.8087</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5021</v>
+        <v>3.3774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0502</v>
+        <v>-5.1861</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9516</v>
+        <v>1.463</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8332</v>
+        <v>4.1209</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1184</v>
+        <v>-2.658</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3993</v>
+        <v>-3.2717</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3311</v>
+        <v>-0.7435</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0682</v>
+        <v>-2.5281</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-4.3122</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>3.6962</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6299</v>
+        <v>1.7978</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4992</v>
+        <v>0.5848</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1307</v>
+        <v>1.2129</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.6447</v>
+        <v>1.8993</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1088</v>
+        <v>1.8993</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.5359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5681</v>
+        <v>0.7068</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3065</v>
+        <v>-1.5482</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8746</v>
+        <v>2.255</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8087</v>
+        <v>-1.0633</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3774</v>
+        <v>-0.0843</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.1861</v>
+        <v>-0.979</v>
       </c>
       <c r="J6" t="n">
-        <v>1.463</v>
+        <v>0.3147</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1209</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.658</v>
+        <v>-0.2372</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2717</v>
+        <v>-1.378</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7435</v>
+        <v>-0.6362</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5281</v>
+        <v>-0.7418</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.616</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3122</v>
+        <v>-3.2855</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6962</v>
+        <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0935</v>
+        <v>1.0432</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3566</v>
+        <v>0.244</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4501</v>
+        <v>0.7992</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8993</v>
+        <v>2.575</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8993</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.3963</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2148</v>
+        <v>0.7065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3857</v>
+        <v>0.6995</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1709</v>
+        <v>0.007</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1642</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2185</v>
+        <v>0.2731</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1976</v>
+        <v>0.1162</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0209</v>
+        <v>0.157</v>
       </c>
       <c r="V7" t="n">
         <v>2.0082</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1004</v>
+        <v>0.0311</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.385</v>
+        <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2846</v>
+        <v>-0.2488</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0633</v>
+        <v>0.8195</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0843</v>
+        <v>0.9145</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.979</v>
+        <v>-0.095</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3147</v>
+        <v>2.1553</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.6034</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2372</v>
+        <v>1.5518</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.378</v>
+        <v>-1.3358</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6362</v>
+        <v>0.311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7418</v>
+        <v>-1.6468</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2855</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S8" t="n">
-        <v>0.236</v>
+        <v>0.4601</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5928</v>
+        <v>0.1781</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8288</v>
+        <v>0.282</v>
       </c>
       <c r="V8" t="n">
-        <v>2.575</v>
+        <v>-1.6591</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.3963</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.886</v>
+        <v>-0.6589</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.048</v>
+        <v>1.2692</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1621</v>
+        <v>-1.9282</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.8943</v>
+        <v>1.5523</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0423</v>
+        <v>1.5021</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.852</v>
+        <v>0.0502</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9668</v>
+        <v>1.9516</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7042</v>
+        <v>1.8332</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.671</v>
+        <v>0.1184</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9275</v>
+        <v>-0.3993</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.3311</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.181</v>
+        <v>-0.0682</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2588</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7476</v>
+        <v>1.2282</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9989</v>
+        <v>0.4532</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7487</v>
+        <v>0.775</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8768</v>
+        <v>-3.6447</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1786</v>
+        <v>-0.1088</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6982</v>
+        <v>-3.5359</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3096</v>
+        <v>-1.7681</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5569</v>
+        <v>-1.9894</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7527</v>
+        <v>0.2213</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8195</v>
+        <v>-4.8943</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9145</v>
+        <v>-0.0423</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.095</v>
+        <v>-4.852</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1553</v>
+        <v>-1.9668</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6034</v>
+        <v>0.7042</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5518</v>
+        <v>-2.671</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3358</v>
+        <v>-2.9275</v>
       </c>
       <c r="N10" t="n">
-        <v>0.311</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6468</v>
+        <v>-2.181</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-2.2588</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4641</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8807</v>
+        <v>1.8655</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6587</v>
+        <v>1.0575</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2219</v>
+        <v>0.8079</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6591</v>
+        <v>1.8768</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6591</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.0755</v>
+        <v>9.075700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>6.066400000000001</v>
+        <v>6.066500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0091</v>
+        <v>3.009</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1068</v>
@@ -1291,7 +1291,7 @@
         <v>15.964</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7126000000000001</v>
+        <v>-0.7125999999999997</v>
       </c>
       <c r="M11" t="n">
         <v>-16.3583</v>
@@ -1312,22 +1312,22 @@
         <v>18.4809</v>
       </c>
       <c r="S11" t="n">
-        <v>9.899000000000001</v>
+        <v>9.8992</v>
       </c>
       <c r="T11" t="n">
-        <v>4.493300000000001</v>
+        <v>4.4932</v>
       </c>
       <c r="U11" t="n">
-        <v>5.4061</v>
+        <v>5.406000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.310100000000001</v>
+        <v>1.3101</v>
       </c>
       <c r="W11" t="n">
         <v>5.8293</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.519299999999999</v>
+        <v>-4.5193</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6242</v>
+        <v>3.537</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4065</v>
+        <v>2.6157</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2177</v>
+        <v>0.9213</v>
       </c>
       <c r="G12" t="n">
         <v>0.3561</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3603</v>
+        <v>-0.4475</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2326</v>
+        <v>-0.0638</v>
       </c>
       <c r="V12" t="n">
         <v>1.9856</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6915</v>
+        <v>2.554</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4726</v>
+        <v>2.4142</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2189</v>
+        <v>0.1398</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8243</v>
+        <v>3.0096</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2905</v>
+        <v>0.652</v>
       </c>
       <c r="I13" t="n">
-        <v>6.1149</v>
+        <v>2.3576</v>
       </c>
       <c r="J13" t="n">
-        <v>6.7043</v>
+        <v>3.5615</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4293</v>
+        <v>2.1802</v>
       </c>
       <c r="L13" t="n">
-        <v>6.2751</v>
+        <v>1.3813</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.88</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7198</v>
+        <v>-1.5282</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1602</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.2855</v>
+        <v>-0.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2855</v>
+        <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9543</v>
+        <v>-1.1332</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4883</v>
+        <v>-0.5928</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4659</v>
+        <v>-0.5404</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4579</v>
+        <v>-0.3491</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.7207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3761</v>
+        <v>2.3933</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4142</v>
+        <v>2.2634</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0381</v>
+        <v>0.1299</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0096</v>
+        <v>4.8243</v>
       </c>
       <c r="H14" t="n">
-        <v>0.652</v>
+        <v>-1.2905</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3576</v>
+        <v>6.1149</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5615</v>
+        <v>6.7043</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1802</v>
+        <v>0.4293</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3813</v>
+        <v>6.2751</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.88</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5282</v>
+        <v>-1.7198</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.1602</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0267</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>-3.2855</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>3.2855</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3111</v>
+        <v>-1.2524</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5928</v>
+        <v>-0.6975</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7183</v>
+        <v>-0.5548</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3491</v>
+        <v>-1.1786</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3491</v>
+        <v>-0.4579</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VENTURA PEDREÑO</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.037</v>
+        <v>-0.8439</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6208</v>
+        <v>1.4323</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5839</v>
+        <v>-2.2762</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4806</v>
+        <v>1.0742</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0227</v>
+        <v>-3.0724</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4579</v>
+        <v>4.1466</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5265</v>
+        <v>3.9328</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1714</v>
+        <v>-0.9081</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6449</v>
+        <v>4.8409</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0071</v>
+        <v>-2.8586</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.194</v>
+        <v>-2.1643</v>
       </c>
       <c r="O15" t="n">
-        <v>0.187</v>
+        <v>-0.6943</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>-5.3389</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3471</v>
+        <v>-1.8461</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6042</v>
+        <v>-0.9378</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2571</v>
+        <v>-0.9084</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6982</v>
+        <v>2.5975</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6982</v>
+        <v>3.7761</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3356</v>
+        <v>-1.0833</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1185</v>
+        <v>-1.3481</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4541</v>
+        <v>0.2648</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0742</v>
+        <v>1.4273</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.0724</v>
+        <v>-0.4804</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1466</v>
+        <v>1.9078</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9328</v>
+        <v>2.2474</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9081</v>
+        <v>0.1557</v>
       </c>
       <c r="L16" t="n">
-        <v>4.8409</v>
+        <v>2.0917</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8586</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1643</v>
+        <v>-0.6362</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6943</v>
+        <v>-0.1839</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.6694</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.3389</v>
+        <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6694</v>
+        <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3378</v>
+        <v>-1.2436</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2516</v>
+        <v>-0.5154</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0862</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5975</v>
+        <v>-0.2402</v>
       </c>
       <c r="W16" t="n">
-        <v>3.7761</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.411</v>
+        <v>-1.1453</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5573</v>
+        <v>-0.8639</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1463</v>
+        <v>-0.2814</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4273</v>
+        <v>-1.8221</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4804</v>
+        <v>-1.5669</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9078</v>
+        <v>-0.2552</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2474</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1557</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0917</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-1.1442</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6362</v>
+        <v>-0.889</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1839</v>
+        <v>-0.2552</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0534</v>
+        <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5714</v>
+        <v>-0.2267</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7246</v>
+        <v>-0.186</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8468</v>
+        <v>-0.0407</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4138</v>
+        <v>-1.8429</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0731</v>
+        <v>-0.6508</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3406</v>
+        <v>-1.1921</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8221</v>
+        <v>-0.3456</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5669</v>
+        <v>-1.1583</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2552</v>
+        <v>0.8127</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.0347</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.0618</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.9729</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1442</v>
+        <v>-1.3803</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.889</v>
+        <v>-1.2201</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2552</v>
+        <v>-0.1602</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4952</v>
+        <v>-1.3454</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3952</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0999</v>
+        <v>-0.6866</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>A. VENTURA PEDREÑO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.768</v>
+        <v>-1.9924</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5462</v>
+        <v>-2.4577</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2217</v>
+        <v>0.4653</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3456</v>
+        <v>-0.4806</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1583</v>
+        <v>-0.0227</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8127</v>
+        <v>-0.4579</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0347</v>
+        <v>0.5265</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0618</v>
+        <v>1.1714</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9729</v>
+        <v>-0.6449</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3803</v>
+        <v>-1.0071</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2201</v>
+        <v>-1.194</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1602</v>
+        <v>0.187</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2704</v>
+        <v>-0.6083</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5542</v>
+        <v>-0.2326</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.3757</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1786</v>
+        <v>-0.6982</v>
       </c>
       <c r="W19" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4057</v>
+        <v>-2.2575</v>
       </c>
       <c r="E20" t="n">
         <v>-2.6863</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2806</v>
+        <v>0.4288</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5901</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.6325</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4611</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3196</v>
+        <v>-0.1714</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7618</v>
+        <v>-4.1646</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3518</v>
+        <v>-1.6656</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.41</v>
+        <v>-2.4989</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1554</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1615</v>
+        <v>-0.2412</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1704</v>
+        <v>-0.1434</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0089</v>
+        <v>-0.0978</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6345</v>
+        <v>-4.2301</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5853</v>
+        <v>-2.0623</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0492</v>
+        <v>-2.1678</v>
       </c>
       <c r="G22" t="n">
         <v>-2.191</v>
@@ -2170,13 +2170,13 @@
         <v>2.4641</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3266</v>
+        <v>-0.9221</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1198</v>
+        <v>-0.5968</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2067</v>
+        <v>-0.3253</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5277</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.075600000000001</v>
+        <v>-9.075700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.009</v>
+        <v>-3.009100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.0663</v>
+        <v>-6.0665</v>
       </c>
       <c r="G23" t="n">
-        <v>1.106699999999999</v>
+        <v>1.106700000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-12.2463</v>
@@ -2224,7 +2224,7 @@
         <v>16.3582</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7177</v>
+        <v>3.717699999999999</v>
       </c>
       <c r="L23" t="n">
         <v>12.6407</v>
@@ -2236,7 +2236,7 @@
         <v>-15.9639</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7127</v>
+        <v>0.7126999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>1.0267</v>
@@ -2248,13 +2248,13 @@
         <v>19.5075</v>
       </c>
       <c r="S23" t="n">
-        <v>-9.8992</v>
+        <v>-9.898999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.4058</v>
+        <v>-5.405799999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.492999999999999</v>
+        <v>-4.493200000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3099</v>
@@ -2263,7 +2263,7 @@
         <v>4.5193</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.8292</v>
+        <v>-5.829200000000001</v>
       </c>
     </row>
   </sheetData>
